--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_06-04-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_06-04-2026.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£13.49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£20.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£38.75</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178204256</t>
+          <t>£31.75</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>£58.12</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>£38.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£78.14</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£58.50</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£53.99</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£110.40</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
